--- a/data/nma/MRI T1 outcomes.xlsx
+++ b/data/nma/MRI T1 outcomes.xlsx
@@ -3211,8 +3211,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1dd74ed78a59e353fa0bdc00cb9d4ef2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29b19980e720fd97176dcdbc89cda831" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="904d962808a52fea145147f501824070">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea18719b0589a0490468c8ade8a27c2" ns2:_="" ns3:_="">
     <xsd:import namespace="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
     <xsd:import namespace="adc125f1-7df9-46f4-a9a7-022dd426a2bb"/>
     <xsd:element name="properties">
@@ -3430,10 +3430,24 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a4e98822-f433-4c96-8830-5cb2d7491f7d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{229B1431-CB6E-4A9F-9D9A-E7B756AB0AB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACBB161A-780A-4773-93F6-78ABF17FF0B9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1736C92E-FE5B-47B5-B22D-C61525EA8E36}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49692E39-BEFE-4741-A0FF-735BEEEED0AB}"/>
 </file>